--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run7/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run7/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,775 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,0,1,1</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
   </si>
   <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.7294,0.0641,0.0235,0.1621</t>
-  </si>
-  <si>
-    <t>0.0296,0.0204,0.0190,0.9705</t>
-  </si>
-  <si>
-    <t>0.7799,0.0290,0.0260,0.1487</t>
-  </si>
-  <si>
-    <t>0.1208,0.0066,0.0048,0.9483</t>
-  </si>
-  <si>
-    <t>0.9957,0.0013,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.9830,0.0135,0.0016,0.0021</t>
-  </si>
-  <si>
-    <t>0.9797,0.0222,0.0021,0.0011</t>
-  </si>
-  <si>
-    <t>0.9834,0.0080,0.0018,0.0027</t>
-  </si>
-  <si>
-    <t>0.9941,0.0020,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9861,0.0171,0.0021,0.0007</t>
-  </si>
-  <si>
-    <t>0.9912,0.0043,0.0003,0.0015</t>
-  </si>
-  <si>
-    <t>0.9826,0.0091,0.0026,0.0028</t>
-  </si>
-  <si>
-    <t>0.4106,0.0194,0.7004,0.0158</t>
-  </si>
-  <si>
-    <t>0.0954,0.0094,0.9380,0.0017</t>
-  </si>
-  <si>
-    <t>0.1005,0.0384,0.8931,0.0004</t>
-  </si>
-  <si>
-    <t>0.0843,0.0412,0.8841,0.0067</t>
-  </si>
-  <si>
-    <t>0.6608,0.0196,0.4678,0.0198</t>
-  </si>
-  <si>
-    <t>0.3539,0.7789,0.0060,0.0024</t>
-  </si>
-  <si>
-    <t>0.3137,0.8158,0.0011,0.0014</t>
-  </si>
-  <si>
-    <t>0.7147,0.4875,0.0022,0.0022</t>
-  </si>
-  <si>
-    <t>0.6500,0.6351,0.0014,0.0007</t>
-  </si>
-  <si>
-    <t>0.0561,0.9529,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.0950,0.0058,0.9124,0.0116</t>
-  </si>
-  <si>
-    <t>0.3851,0.0097,0.6945,0.0269</t>
-  </si>
-  <si>
-    <t>0.0173,0.0030,0.9745,0.0054</t>
-  </si>
-  <si>
-    <t>0.2602,0.0253,0.8044,0.0076</t>
-  </si>
-  <si>
-    <t>0.0144,0.0069,0.9773,0.0057</t>
-  </si>
-  <si>
-    <t>0.0223,0.0080,0.9143,0.0635</t>
-  </si>
-  <si>
-    <t>0.0035,0.0022,0.9969,0.0001</t>
-  </si>
-  <si>
-    <t>0.4457,0.6716,0.0144,0.0026</t>
-  </si>
-  <si>
-    <t>0.4623,0.0258,0.6762,0.0030</t>
-  </si>
-  <si>
-    <t>0.0076,0.0266,0.9794,0.0063</t>
-  </si>
-  <si>
-    <t>0.0251,0.8498,0.2024,0.0025</t>
-  </si>
-  <si>
-    <t>0.6836,0.1903,0.0426,0.1300</t>
-  </si>
-  <si>
-    <t>0.5668,0.3884,0.0851,0.0054</t>
-  </si>
-  <si>
-    <t>0.7019,0.4424,0.0130,0.0057</t>
-  </si>
-  <si>
-    <t>0.0221,0.9349,0.1343,0.0041</t>
-  </si>
-  <si>
-    <t>0.0080,0.8012,0.0323,0.3909</t>
-  </si>
-  <si>
-    <t>0.0225,0.0183,0.6073,0.5099</t>
-  </si>
-  <si>
-    <t>0.0317,0.1472,0.8301,0.0693</t>
-  </si>
-  <si>
-    <t>0.0374,0.0110,0.6495,0.4700</t>
-  </si>
-  <si>
-    <t>0.0290,0.1229,0.9270,0.0049</t>
-  </si>
-  <si>
-    <t>0.0036,0.9840,0.0085,0.0003</t>
-  </si>
-  <si>
-    <t>0.0033,0.0818,0.9714,0.0080</t>
-  </si>
-  <si>
-    <t>0.1222,0.3923,0.0163,0.7476</t>
-  </si>
-  <si>
-    <t>0.0084,0.9483,0.1099,0.0234</t>
-  </si>
-  <si>
-    <t>0.0196,0.9284,0.1092,0.0039</t>
-  </si>
-  <si>
-    <t>0.0044,0.9727,0.0898,0.0043</t>
-  </si>
-  <si>
-    <t>0.0031,0.2428,0.9649,0.0053</t>
-  </si>
-  <si>
-    <t>0.0002,0.0646,0.9957,0.0003</t>
-  </si>
-  <si>
-    <t>0.0571,0.0459,0.9221,0.0054</t>
-  </si>
-  <si>
-    <t>0.0251,0.0109,0.9562,0.0097</t>
-  </si>
-  <si>
-    <t>0.0007,0.0038,0.9940,0.0031</t>
-  </si>
-  <si>
-    <t>0.0012,0.0085,0.9948,0.0007</t>
-  </si>
-  <si>
-    <t>0.9541,0.0338,0.0065,0.0063</t>
-  </si>
-  <si>
-    <t>0.9738,0.0086,0.0014,0.0066</t>
-  </si>
-  <si>
-    <t>0.9605,0.0338,0.0158,0.0022</t>
-  </si>
-  <si>
-    <t>0.0018,0.0300,0.9887,0.0038</t>
-  </si>
-  <si>
-    <t>0.9833,0.0073,0.0004,0.0025</t>
-  </si>
-  <si>
-    <t>0.9601,0.0539,0.0061,0.0011</t>
-  </si>
-  <si>
-    <t>0.9726,0.0326,0.0043,0.0008</t>
-  </si>
-  <si>
-    <t>0.0045,0.9319,0.4608,0.0053</t>
-  </si>
-  <si>
-    <t>0.0057,0.0778,0.9412,0.0202</t>
-  </si>
-  <si>
-    <t>0.0039,0.1191,0.9195,0.0502</t>
-  </si>
-  <si>
-    <t>0.0026,0.7113,0.9398,0.0013</t>
-  </si>
-  <si>
-    <t>0.0004,0.0271,0.9930,0.0013</t>
-  </si>
-  <si>
-    <t>0.0179,0.8983,0.1251,0.0018</t>
-  </si>
-  <si>
-    <t>0.0048,0.9902,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.8215,0.0309,0.2562,0.0061</t>
-  </si>
-  <si>
-    <t>0.2997,0.4673,0.3667,0.0129</t>
-  </si>
-  <si>
-    <t>0.0104,0.0380,0.9808,0.0004</t>
-  </si>
-  <si>
-    <t>0.0041,0.8589,0.6676,0.0013</t>
-  </si>
-  <si>
-    <t>0.0009,0.7972,0.8719,0.0001</t>
-  </si>
-  <si>
-    <t>0.0027,0.9647,0.0904,0.0004</t>
-  </si>
-  <si>
-    <t>0.0009,0.8891,0.8024,0.0009</t>
-  </si>
-  <si>
-    <t>0.1462,0.0024,0.1810,0.6635</t>
-  </si>
-  <si>
-    <t>0.0075,0.0091,0.0006,0.9945</t>
-  </si>
-  <si>
-    <t>0.0017,0.0065,0.0006,0.9979</t>
-  </si>
-  <si>
-    <t>0.0149,0.0061,0.0235,0.9812</t>
-  </si>
-  <si>
-    <t>0.0091,0.0133,0.0208,0.9855</t>
-  </si>
-  <si>
-    <t>0.0178,0.0112,0.0067,0.9849</t>
-  </si>
-  <si>
-    <t>0.0006,0.9073,0.9387,0.0003</t>
-  </si>
-  <si>
-    <t>0.0022,0.3417,0.9645,0.0042</t>
-  </si>
-  <si>
-    <t>0.0032,0.4406,0.9323,0.0021</t>
-  </si>
-  <si>
-    <t>0.0026,0.3144,0.9583,0.0010</t>
-  </si>
-  <si>
-    <t>0.0011,0.9744,0.2127,0.0001</t>
-  </si>
-  <si>
-    <t>0.0026,0.6628,0.9021,0.0005</t>
-  </si>
-  <si>
-    <t>0.9588,0.0237,0.0176,0.0060</t>
-  </si>
-  <si>
-    <t>0.9702,0.0641,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.9691,0.0318,0.0024,0.0021</t>
-  </si>
-  <si>
-    <t>0.9900,0.0021,0.0003,0.0034</t>
-  </si>
-  <si>
-    <t>0.9747,0.0444,0.0009,0.0006</t>
-  </si>
-  <si>
-    <t>0.9867,0.0055,0.0002,0.0022</t>
-  </si>
-  <si>
-    <t>0.9828,0.0117,0.0004,0.0020</t>
-  </si>
-  <si>
-    <t>0.9520,0.0801,0.0036,0.0005</t>
-  </si>
-  <si>
-    <t>0.9940,0.0009,0.0000,0.0019</t>
-  </si>
-  <si>
-    <t>0.9943,0.0028,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.9946,0.0028,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9918,0.0044,0.0009,0.0012</t>
-  </si>
-  <si>
-    <t>0.9915,0.0052,0.0009,0.0010</t>
-  </si>
-  <si>
-    <t>0.9905,0.0039,0.0003,0.0015</t>
-  </si>
-  <si>
-    <t>0.9929,0.0025,0.0002,0.0013</t>
-  </si>
-  <si>
-    <t>0.9831,0.0067,0.0007,0.0036</t>
-  </si>
-  <si>
-    <t>0.0002,0.0021,0.9982,0.0008</t>
-  </si>
-  <si>
-    <t>0.1064,0.0090,0.9214,0.0051</t>
-  </si>
-  <si>
-    <t>0.6671,0.0035,0.3160,0.0473</t>
-  </si>
-  <si>
-    <t>0.0177,0.0068,0.9752,0.0046</t>
-  </si>
-  <si>
-    <t>0.1136,0.8783,0.0189,0.0048</t>
-  </si>
-  <si>
-    <t>0.0152,0.9723,0.0030,0.0012</t>
-  </si>
-  <si>
-    <t>0.2992,0.8082,0.0015,0.0024</t>
-  </si>
-  <si>
-    <t>0.3011,0.8012,0.0034,0.0023</t>
-  </si>
-  <si>
-    <t>0.2704,0.7720,0.0174,0.0020</t>
-  </si>
-  <si>
-    <t>0.0576,0.9218,0.0155,0.0009</t>
-  </si>
-  <si>
-    <t>0.6879,0.4746,0.0089,0.0038</t>
-  </si>
-  <si>
-    <t>0.7700,0.0356,0.2694,0.0108</t>
-  </si>
-  <si>
-    <t>0.1865,0.0075,0.8789,0.0068</t>
-  </si>
-  <si>
-    <t>0.6264,0.0898,0.3167,0.0187</t>
-  </si>
-  <si>
-    <t>0.4623,0.0176,0.6162,0.0315</t>
-  </si>
-  <si>
-    <t>0.0577,0.5711,0.0333,0.7894</t>
-  </si>
-  <si>
-    <t>0.0049,0.9770,0.0235,0.0061</t>
-  </si>
-  <si>
-    <t>0.0048,0.9579,0.0531,0.0694</t>
-  </si>
-  <si>
-    <t>0.0643,0.7711,0.0906,0.2999</t>
-  </si>
-  <si>
-    <t>0.0009,0.9418,0.7035,0.0002</t>
-  </si>
-  <si>
-    <t>0.0526,0.9156,0.0689,0.0007</t>
-  </si>
-  <si>
-    <t>0.5493,0.2170,0.1629,0.0020</t>
-  </si>
-  <si>
-    <t>0.4317,0.6379,0.0313,0.0057</t>
-  </si>
-  <si>
-    <t>0.9767,0.0142,0.0051,0.0040</t>
-  </si>
-  <si>
-    <t>0.9837,0.0043,0.0005,0.0048</t>
-  </si>
-  <si>
-    <t>0.9649,0.0171,0.0146,0.0043</t>
-  </si>
-  <si>
-    <t>0.9842,0.0082,0.0006,0.0021</t>
-  </si>
-  <si>
-    <t>0.9815,0.0089,0.0126,0.0009</t>
-  </si>
-  <si>
-    <t>0.9730,0.0255,0.0070,0.0008</t>
-  </si>
-  <si>
-    <t>0.9774,0.0208,0.0041,0.0015</t>
-  </si>
-  <si>
-    <t>0.9835,0.0192,0.0024,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.8306,0.9113,0.0001</t>
-  </si>
-  <si>
-    <t>0.0095,0.5922,0.8289,0.0026</t>
-  </si>
-  <si>
-    <t>0.0084,0.0774,0.9531,0.0011</t>
-  </si>
-  <si>
-    <t>0.0499,0.0983,0.8979,0.0040</t>
-  </si>
-  <si>
-    <t>0.7280,0.1259,0.1373,0.0294</t>
-  </si>
-  <si>
-    <t>0.5461,0.1145,0.3806,0.1094</t>
-  </si>
-  <si>
-    <t>0.5402,0.0024,0.7695,0.0012</t>
-  </si>
-  <si>
-    <t>0.5704,0.1857,0.3085,0.0333</t>
-  </si>
-  <si>
-    <t>0.0317,0.0049,0.0158,0.9739</t>
-  </si>
-  <si>
-    <t>0.0011,0.0030,0.0055,0.9972</t>
-  </si>
-  <si>
-    <t>0.0018,0.0139,0.0308,0.9918</t>
-  </si>
-  <si>
-    <t>0.0206,0.0037,0.0024,0.9880</t>
-  </si>
-  <si>
-    <t>0.0004,0.9387,0.7416,0.0003</t>
-  </si>
-  <si>
-    <t>0.9723,0.0265,0.0021,0.0025</t>
-  </si>
-  <si>
-    <t>0.6618,0.4908,0.0061,0.0019</t>
-  </si>
-  <si>
-    <t>0.9523,0.0787,0.0011,0.0011</t>
-  </si>
-  <si>
-    <t>0.9288,0.1204,0.0038,0.0008</t>
-  </si>
-  <si>
-    <t>0.9573,0.0166,0.0060,0.0091</t>
-  </si>
-  <si>
-    <t>0.3205,0.0167,0.0547,0.7249</t>
-  </si>
-  <si>
-    <t>0.9773,0.0054,0.0013,0.0069</t>
-  </si>
-  <si>
-    <t>0.0010,0.0339,0.9706,0.0413</t>
-  </si>
-  <si>
-    <t>0.6098,0.0024,0.0749,0.2370</t>
-  </si>
-  <si>
-    <t>0.8961,0.0060,0.0040,0.0995</t>
-  </si>
-  <si>
-    <t>0.7504,0.1683,0.1019,0.0133</t>
-  </si>
-  <si>
-    <t>0.8736,0.1161,0.0050,0.0083</t>
-  </si>
-  <si>
-    <t>0.7788,0.2100,0.0599,0.0213</t>
-  </si>
-  <si>
-    <t>0.7212,0.1000,0.1378,0.0663</t>
-  </si>
-  <si>
-    <t>0.6666,0.2159,0.1646,0.0094</t>
-  </si>
-  <si>
-    <t>0.7021,0.1657,0.1850,0.0120</t>
-  </si>
-  <si>
-    <t>0.9547,0.0207,0.0269,0.0053</t>
-  </si>
-  <si>
-    <t>0.9729,0.0054,0.0004,0.0103</t>
-  </si>
-  <si>
-    <t>0.9811,0.0047,0.0007,0.0055</t>
-  </si>
-  <si>
-    <t>0.9848,0.0091,0.0018,0.0017</t>
-  </si>
-  <si>
-    <t>0.9718,0.0081,0.0049,0.0103</t>
-  </si>
-  <si>
-    <t>0.9862,0.0071,0.0010,0.0020</t>
-  </si>
-  <si>
-    <t>0.9805,0.0033,0.0008,0.0087</t>
-  </si>
-  <si>
-    <t>0.9909,0.0038,0.0004,0.0014</t>
-  </si>
-  <si>
-    <t>0.4687,0.6222,0.0134,0.0124</t>
-  </si>
-  <si>
-    <t>0.7963,0.3036,0.0135,0.0029</t>
-  </si>
-  <si>
-    <t>0.8723,0.2117,0.0024,0.0022</t>
-  </si>
-  <si>
-    <t>0.8542,0.1106,0.0539,0.0085</t>
-  </si>
-  <si>
-    <t>0.9094,0.1528,0.0039,0.0025</t>
-  </si>
-  <si>
-    <t>0.9420,0.0362,0.0247,0.0028</t>
-  </si>
-  <si>
-    <t>0.9706,0.0508,0.0007,0.0007</t>
-  </si>
-  <si>
-    <t>0.6589,0.4532,0.0197,0.0044</t>
-  </si>
-  <si>
-    <t>0.0045,0.1693,0.9525,0.0001</t>
-  </si>
-  <si>
-    <t>0.9408,0.0897,0.0045,0.0010</t>
-  </si>
-  <si>
-    <t>0.0013,0.0040,0.9973,0.0002</t>
-  </si>
-  <si>
-    <t>0.0217,0.1215,0.9303,0.0233</t>
-  </si>
-  <si>
-    <t>0.0548,0.0195,0.9511,0.0012</t>
-  </si>
-  <si>
-    <t>0.0085,0.0827,0.9606,0.0090</t>
-  </si>
-  <si>
-    <t>0.0033,0.0174,0.9913,0.0007</t>
-  </si>
-  <si>
-    <t>0.0116,0.0018,0.9931,0.0001</t>
-  </si>
-  <si>
-    <t>0.0022,0.0049,0.9944,0.0007</t>
-  </si>
-  <si>
-    <t>0.2539,0.1718,0.5454,0.0124</t>
-  </si>
-  <si>
-    <t>0.2298,0.0232,0.8471,0.0032</t>
-  </si>
-  <si>
-    <t>0.5128,0.3845,0.1232,0.0113</t>
-  </si>
-  <si>
-    <t>0.4854,0.0321,0.6019,0.0032</t>
-  </si>
-  <si>
-    <t>0.0263,0.3363,0.7908,0.0008</t>
-  </si>
-  <si>
-    <t>0.6026,0.1901,0.2059,0.0055</t>
-  </si>
-  <si>
-    <t>0.4994,0.1327,0.4493,0.0179</t>
-  </si>
-  <si>
-    <t>0.2103,0.0950,0.7675,0.0096</t>
-  </si>
-  <si>
-    <t>0.7450,0.3856,0.0077,0.0008</t>
-  </si>
-  <si>
-    <t>0.8722,0.2244,0.0039,0.0004</t>
-  </si>
-  <si>
-    <t>0.8963,0.1190,0.0194,0.0015</t>
-  </si>
-  <si>
-    <t>0.9772,0.0393,0.0023,0.0004</t>
-  </si>
-  <si>
-    <t>0.6166,0.5502,0.0040,0.0019</t>
-  </si>
-  <si>
-    <t>0.5035,0.2005,0.3082,0.0768</t>
-  </si>
-  <si>
-    <t>0.7942,0.0158,0.1728,0.0275</t>
-  </si>
-  <si>
-    <t>0.7807,0.0305,0.0545,0.0613</t>
-  </si>
-  <si>
-    <t>0.5692,0.0052,0.5919,0.0159</t>
-  </si>
-  <si>
-    <t>0.5855,0.0053,0.5519,0.0246</t>
-  </si>
-  <si>
-    <t>0.0385,0.0288,0.8954,0.0640</t>
-  </si>
-  <si>
-    <t>0.0184,0.2602,0.8264,0.0460</t>
-  </si>
-  <si>
-    <t>0.0180,0.2249,0.9150,0.0038</t>
-  </si>
-  <si>
-    <t>0.1478,0.0889,0.7527,0.0801</t>
-  </si>
-  <si>
-    <t>0.0043,0.0436,0.9749,0.0033</t>
-  </si>
-  <si>
-    <t>0.9919,0.0027,0.0002,0.0014</t>
-  </si>
-  <si>
-    <t>0.9845,0.0230,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9927,0.0046,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.9757,0.0334,0.0017,0.0010</t>
-  </si>
-  <si>
-    <t>0.9894,0.0096,0.0008,0.0008</t>
-  </si>
-  <si>
-    <t>0.9910,0.0075,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.9859,0.0032,0.0009,0.0052</t>
-  </si>
-  <si>
-    <t>0.9893,0.0044,0.0003,0.0017</t>
-  </si>
-  <si>
-    <t>0.0257,0.0074,0.9752,0.0026</t>
-  </si>
-  <si>
-    <t>0.2898,0.0871,0.7037,0.0086</t>
-  </si>
-  <si>
-    <t>0.9185,0.0450,0.0056,0.0212</t>
-  </si>
-  <si>
-    <t>0.0011,0.0053,0.9958,0.0006</t>
-  </si>
-  <si>
-    <t>0.0018,0.0156,0.9903,0.0016</t>
-  </si>
-  <si>
-    <t>0.0061,0.0342,0.9895,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0112,0.9953,0.0009</t>
-  </si>
-  <si>
-    <t>0.1546,0.0620,0.7773,0.0086</t>
-  </si>
-  <si>
-    <t>0.0032,0.0279,0.9854,0.0023</t>
-  </si>
-  <si>
-    <t>0.0030,0.0290,0.9801,0.0029</t>
-  </si>
-  <si>
-    <t>0.0492,0.0511,0.9293,0.0015</t>
-  </si>
-  <si>
-    <t>0.7888,0.0065,0.1767,0.0331</t>
-  </si>
-  <si>
-    <t>0.6508,0.0135,0.4086,0.0359</t>
-  </si>
-  <si>
-    <t>0.8320,0.0092,0.1807,0.0122</t>
-  </si>
-  <si>
-    <t>0.9857,0.0126,0.0019,0.0010</t>
-  </si>
-  <si>
-    <t>0.9843,0.0092,0.0025,0.0019</t>
-  </si>
-  <si>
-    <t>0.9914,0.0051,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.9777,0.0181,0.0017,0.0026</t>
-  </si>
-  <si>
-    <t>0.9720,0.0242,0.0012,0.0029</t>
-  </si>
-  <si>
-    <t>0.9701,0.0399,0.0013,0.0010</t>
-  </si>
-  <si>
-    <t>0.9913,0.0027,0.0002,0.0022</t>
-  </si>
-  <si>
-    <t>0.9819,0.0033,0.0003,0.0079</t>
-  </si>
-  <si>
-    <t>0.0220,0.3183,0.7923,0.0019</t>
-  </si>
-  <si>
-    <t>0.0011,0.0234,0.9912,0.0013</t>
-  </si>
-  <si>
-    <t>0.0180,0.0341,0.9635,0.0058</t>
-  </si>
-  <si>
-    <t>0.0717,0.0971,0.8058,0.0048</t>
-  </si>
-  <si>
-    <t>0.0113,0.0270,0.9755,0.0053</t>
-  </si>
-  <si>
-    <t>0.1823,0.0073,0.1312,0.7091</t>
-  </si>
-  <si>
-    <t>0.1818,0.0366,0.7992,0.0118</t>
-  </si>
-  <si>
-    <t>0.0094,0.0269,0.7409,0.4117</t>
-  </si>
-  <si>
-    <t>0.8870,0.0018,0.0013,0.1652</t>
-  </si>
-  <si>
-    <t>0.0174,0.0457,0.0119,0.9804</t>
-  </si>
-  <si>
-    <t>0.1578,0.0072,0.0371,0.8797</t>
-  </si>
-  <si>
-    <t>0.0043,0.0010,0.0025,0.9959</t>
-  </si>
-  <si>
-    <t>0.0054,0.0014,0.0031,0.9945</t>
-  </si>
-  <si>
-    <t>0.7547,0.0197,0.0459,0.1719</t>
+    <t>0.6090,0.0745,0.1016,0.2496</t>
+  </si>
+  <si>
+    <t>0.0579,0.0029,0.0056,0.9719</t>
+  </si>
+  <si>
+    <t>0.4997,0.0188,0.0104,0.6490</t>
+  </si>
+  <si>
+    <t>0.0456,0.0355,0.0019,0.9686</t>
+  </si>
+  <si>
+    <t>0.9942,0.0017,0.0000,0.0013</t>
+  </si>
+  <si>
+    <t>0.9941,0.0021,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.9739,0.0352,0.0028,0.0010</t>
+  </si>
+  <si>
+    <t>0.9926,0.0013,0.0002,0.0025</t>
+  </si>
+  <si>
+    <t>0.9862,0.0111,0.0006,0.0015</t>
+  </si>
+  <si>
+    <t>0.9927,0.0025,0.0001,0.0013</t>
+  </si>
+  <si>
+    <t>0.9918,0.0023,0.0001,0.0019</t>
+  </si>
+  <si>
+    <t>0.9940,0.0028,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.4116,0.0183,0.7176,0.0050</t>
+  </si>
+  <si>
+    <t>0.1212,0.0084,0.9491,0.0004</t>
+  </si>
+  <si>
+    <t>0.4400,0.0182,0.6892,0.0032</t>
+  </si>
+  <si>
+    <t>0.0777,0.0493,0.9018,0.0020</t>
+  </si>
+  <si>
+    <t>0.7940,0.0241,0.2838,0.0027</t>
+  </si>
+  <si>
+    <t>0.0779,0.9237,0.0078,0.0004</t>
+  </si>
+  <si>
+    <t>0.1556,0.9109,0.0022,0.0002</t>
+  </si>
+  <si>
+    <t>0.8106,0.2815,0.0065,0.0036</t>
+  </si>
+  <si>
+    <t>0.2005,0.8834,0.0030,0.0004</t>
+  </si>
+  <si>
+    <t>0.0711,0.9359,0.0075,0.0004</t>
+  </si>
+  <si>
+    <t>0.3066,0.0021,0.8136,0.0098</t>
+  </si>
+  <si>
+    <t>0.3828,0.0152,0.6726,0.0342</t>
+  </si>
+  <si>
+    <t>0.0016,0.0052,0.9801,0.0193</t>
+  </si>
+  <si>
+    <t>0.1068,0.0181,0.9108,0.0050</t>
+  </si>
+  <si>
+    <t>0.1731,0.0027,0.9306,0.0012</t>
+  </si>
+  <si>
+    <t>0.0891,0.0011,0.9375,0.0043</t>
+  </si>
+  <si>
+    <t>0.0026,0.0034,0.9958,0.0003</t>
+  </si>
+  <si>
+    <t>0.5327,0.3046,0.1028,0.0019</t>
+  </si>
+  <si>
+    <t>0.5495,0.0717,0.5312,0.0053</t>
+  </si>
+  <si>
+    <t>0.0009,0.0105,0.9950,0.0013</t>
+  </si>
+  <si>
+    <t>0.0775,0.6133,0.2510,0.0024</t>
+  </si>
+  <si>
+    <t>0.8350,0.1231,0.0302,0.0175</t>
+  </si>
+  <si>
+    <t>0.4935,0.1039,0.4638,0.0067</t>
+  </si>
+  <si>
+    <t>0.6166,0.5225,0.0080,0.0054</t>
+  </si>
+  <si>
+    <t>0.0970,0.8602,0.1176,0.0068</t>
+  </si>
+  <si>
+    <t>0.0040,0.9533,0.1238,0.0193</t>
+  </si>
+  <si>
+    <t>0.0336,0.0936,0.5897,0.4040</t>
+  </si>
+  <si>
+    <t>0.0320,0.0583,0.5864,0.4708</t>
+  </si>
+  <si>
+    <t>0.0775,0.0099,0.3186,0.7186</t>
+  </si>
+  <si>
+    <t>0.0135,0.1020,0.9588,0.0035</t>
+  </si>
+  <si>
+    <t>0.0020,0.9861,0.0061,0.0002</t>
+  </si>
+  <si>
+    <t>0.0339,0.2034,0.8663,0.0302</t>
+  </si>
+  <si>
+    <t>0.0904,0.5950,0.1363,0.5997</t>
+  </si>
+  <si>
+    <t>0.0031,0.9840,0.0383,0.0011</t>
+  </si>
+  <si>
+    <t>0.0042,0.9704,0.0758,0.0022</t>
+  </si>
+  <si>
+    <t>0.0040,0.9736,0.0850,0.0014</t>
+  </si>
+  <si>
+    <t>0.0052,0.2537,0.9519,0.0034</t>
+  </si>
+  <si>
+    <t>0.0009,0.1952,0.9914,0.0002</t>
+  </si>
+  <si>
+    <t>0.0183,0.0063,0.9729,0.0041</t>
+  </si>
+  <si>
+    <t>0.0104,0.0092,0.9840,0.0023</t>
+  </si>
+  <si>
+    <t>0.0014,0.0039,0.9934,0.0022</t>
+  </si>
+  <si>
+    <t>0.0132,0.0960,0.9588,0.0013</t>
+  </si>
+  <si>
+    <t>0.9585,0.0657,0.0007,0.0013</t>
+  </si>
+  <si>
+    <t>0.9837,0.0027,0.0003,0.0061</t>
+  </si>
+  <si>
+    <t>0.9716,0.0234,0.0009,0.0025</t>
+  </si>
+  <si>
+    <t>0.0233,0.0793,0.9233,0.0311</t>
+  </si>
+  <si>
+    <t>0.9749,0.0206,0.0045,0.0020</t>
+  </si>
+  <si>
+    <t>0.9679,0.0496,0.0038,0.0009</t>
+  </si>
+  <si>
+    <t>0.9296,0.1252,0.0030,0.0010</t>
+  </si>
+  <si>
+    <t>0.0085,0.6262,0.9154,0.0052</t>
+  </si>
+  <si>
+    <t>0.0022,0.1291,0.9587,0.0151</t>
+  </si>
+  <si>
+    <t>0.0055,0.0588,0.9725,0.0058</t>
+  </si>
+  <si>
+    <t>0.0087,0.7870,0.8833,0.0032</t>
+  </si>
+  <si>
+    <t>0.0038,0.0065,0.9929,0.0009</t>
+  </si>
+  <si>
+    <t>0.0672,0.8619,0.0378,0.0024</t>
+  </si>
+  <si>
+    <t>0.0052,0.9875,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.4598,0.0357,0.6637,0.0041</t>
+  </si>
+  <si>
+    <t>0.6923,0.1436,0.2065,0.0151</t>
+  </si>
+  <si>
+    <t>0.2137,0.1233,0.5262,0.0014</t>
+  </si>
+  <si>
+    <t>0.0016,0.8814,0.8752,0.0007</t>
+  </si>
+  <si>
+    <t>0.0034,0.7747,0.8026,0.0006</t>
+  </si>
+  <si>
+    <t>0.0011,0.9825,0.0636,0.0007</t>
+  </si>
+  <si>
+    <t>0.0003,0.9410,0.6321,0.0001</t>
+  </si>
+  <si>
+    <t>0.0500,0.0090,0.0485,0.9421</t>
+  </si>
+  <si>
+    <t>0.0036,0.0063,0.0025,0.9957</t>
+  </si>
+  <si>
+    <t>0.0146,0.0080,0.0066,0.9880</t>
+  </si>
+  <si>
+    <t>0.0133,0.0046,0.0072,0.9881</t>
+  </si>
+  <si>
+    <t>0.0070,0.0273,0.0056,0.9910</t>
+  </si>
+  <si>
+    <t>0.0053,0.0062,0.0012,0.9959</t>
+  </si>
+  <si>
+    <t>0.0003,0.9792,0.4236,0.0001</t>
+  </si>
+  <si>
+    <t>0.0034,0.4147,0.9625,0.0010</t>
+  </si>
+  <si>
+    <t>0.0162,0.6019,0.7488,0.0065</t>
+  </si>
+  <si>
+    <t>0.0192,0.2104,0.9088,0.0051</t>
+  </si>
+  <si>
+    <t>0.0027,0.8896,0.6580,0.0003</t>
+  </si>
+  <si>
+    <t>0.0020,0.9508,0.2890,0.0002</t>
+  </si>
+  <si>
+    <t>0.9865,0.0041,0.0005,0.0034</t>
+  </si>
+  <si>
+    <t>0.9868,0.0096,0.0004,0.0014</t>
+  </si>
+  <si>
+    <t>0.9588,0.0610,0.0026,0.0010</t>
+  </si>
+  <si>
+    <t>0.9835,0.0032,0.0003,0.0063</t>
+  </si>
+  <si>
+    <t>0.9802,0.0214,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.9900,0.0115,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.9877,0.0137,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9566,0.0934,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9947,0.0010,0.0001,0.0016</t>
+  </si>
+  <si>
+    <t>0.9933,0.0071,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9937,0.0018,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.9959,0.0019,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9878,0.0048,0.0002,0.0022</t>
+  </si>
+  <si>
+    <t>0.9906,0.0084,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.9934,0.0029,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9899,0.0018,0.0001,0.0038</t>
+  </si>
+  <si>
+    <t>0.0038,0.0089,0.9820,0.0100</t>
+  </si>
+  <si>
+    <t>0.0206,0.0109,0.9625,0.0105</t>
+  </si>
+  <si>
+    <t>0.4440,0.0131,0.6081,0.0478</t>
+  </si>
+  <si>
+    <t>0.2285,0.0196,0.8149,0.0033</t>
+  </si>
+  <si>
+    <t>0.0850,0.9183,0.0036,0.0016</t>
+  </si>
+  <si>
+    <t>0.1027,0.9102,0.0046,0.0008</t>
+  </si>
+  <si>
+    <t>0.0720,0.9378,0.0018,0.0007</t>
+  </si>
+  <si>
+    <t>0.2002,0.8603,0.0035,0.0009</t>
+  </si>
+  <si>
+    <t>0.5694,0.5994,0.0076,0.0022</t>
+  </si>
+  <si>
+    <t>0.0182,0.9686,0.0098,0.0007</t>
+  </si>
+  <si>
+    <t>0.8894,0.2386,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.5419,0.1897,0.3275,0.0965</t>
+  </si>
+  <si>
+    <t>0.2332,0.0127,0.8441,0.0083</t>
+  </si>
+  <si>
+    <t>0.1369,0.7630,0.0664,0.0196</t>
+  </si>
+  <si>
+    <t>0.1096,0.0323,0.8917,0.0138</t>
+  </si>
+  <si>
+    <t>0.1632,0.4807,0.0788,0.6830</t>
+  </si>
+  <si>
+    <t>0.0033,0.9863,0.0230,0.0003</t>
+  </si>
+  <si>
+    <t>0.0038,0.9801,0.0292,0.0024</t>
+  </si>
+  <si>
+    <t>0.0208,0.9183,0.1109,0.0361</t>
+  </si>
+  <si>
+    <t>0.0003,0.9740,0.7671,0.0001</t>
+  </si>
+  <si>
+    <t>0.0459,0.9401,0.0353,0.0004</t>
+  </si>
+  <si>
+    <t>0.5729,0.4401,0.0388,0.0014</t>
+  </si>
+  <si>
+    <t>0.7465,0.3842,0.0086,0.0029</t>
+  </si>
+  <si>
+    <t>0.9690,0.0167,0.0138,0.0026</t>
+  </si>
+  <si>
+    <t>0.9841,0.0082,0.0023,0.0023</t>
+  </si>
+  <si>
+    <t>0.9907,0.0028,0.0005,0.0020</t>
+  </si>
+  <si>
+    <t>0.9875,0.0072,0.0006,0.0013</t>
+  </si>
+  <si>
+    <t>0.9950,0.0019,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9734,0.0266,0.0037,0.0018</t>
+  </si>
+  <si>
+    <t>0.9852,0.0043,0.0015,0.0038</t>
+  </si>
+  <si>
+    <t>0.9665,0.0274,0.0039,0.0027</t>
+  </si>
+  <si>
+    <t>0.0012,0.6166,0.9652,0.0006</t>
+  </si>
+  <si>
+    <t>0.0051,0.6055,0.8657,0.0014</t>
+  </si>
+  <si>
+    <t>0.0012,0.2224,0.9760,0.0022</t>
+  </si>
+  <si>
+    <t>0.0031,0.0408,0.9848,0.0006</t>
+  </si>
+  <si>
+    <t>0.6202,0.0357,0.4113,0.0456</t>
+  </si>
+  <si>
+    <t>0.6140,0.1534,0.2470,0.0475</t>
+  </si>
+  <si>
+    <t>0.6024,0.0067,0.5729,0.0164</t>
+  </si>
+  <si>
+    <t>0.6500,0.0542,0.2921,0.0414</t>
+  </si>
+  <si>
+    <t>0.0426,0.0070,0.0126,0.9667</t>
+  </si>
+  <si>
+    <t>0.0015,0.0063,0.0086,0.9959</t>
+  </si>
+  <si>
+    <t>0.0016,0.0078,0.0027,0.9972</t>
+  </si>
+  <si>
+    <t>0.0969,0.0010,0.0033,0.9640</t>
+  </si>
+  <si>
+    <t>0.0012,0.7544,0.9222,0.0006</t>
+  </si>
+  <si>
+    <t>0.9699,0.0271,0.0034,0.0022</t>
+  </si>
+  <si>
+    <t>0.8440,0.2496,0.0049,0.0036</t>
+  </si>
+  <si>
+    <t>0.9609,0.0148,0.0026,0.0108</t>
+  </si>
+  <si>
+    <t>0.9218,0.1148,0.0069,0.0011</t>
+  </si>
+  <si>
+    <t>0.9677,0.0081,0.0047,0.0085</t>
+  </si>
+  <si>
+    <t>0.2046,0.1334,0.0330,0.8125</t>
+  </si>
+  <si>
+    <t>0.9566,0.0273,0.0066,0.0065</t>
+  </si>
+  <si>
+    <t>0.0016,0.1512,0.9758,0.0088</t>
+  </si>
+  <si>
+    <t>0.8210,0.0045,0.0078,0.1775</t>
+  </si>
+  <si>
+    <t>0.9265,0.0262,0.0185,0.0205</t>
+  </si>
+  <si>
+    <t>0.4711,0.5614,0.0309,0.0135</t>
+  </si>
+  <si>
+    <t>0.8591,0.0805,0.0458,0.0164</t>
+  </si>
+  <si>
+    <t>0.7947,0.0999,0.1467,0.0122</t>
+  </si>
+  <si>
+    <t>0.4537,0.5493,0.0252,0.0236</t>
+  </si>
+  <si>
+    <t>0.6088,0.0640,0.4290,0.0085</t>
+  </si>
+  <si>
+    <t>0.6021,0.3895,0.0853,0.0346</t>
+  </si>
+  <si>
+    <t>0.9851,0.0062,0.0006,0.0030</t>
+  </si>
+  <si>
+    <t>0.9855,0.0030,0.0002,0.0055</t>
+  </si>
+  <si>
+    <t>0.9884,0.0062,0.0004,0.0014</t>
+  </si>
+  <si>
+    <t>0.9682,0.0023,0.0010,0.0241</t>
+  </si>
+  <si>
+    <t>0.9857,0.0097,0.0015,0.0013</t>
+  </si>
+  <si>
+    <t>0.9635,0.0406,0.0096,0.0014</t>
+  </si>
+  <si>
+    <t>0.9890,0.0043,0.0009,0.0024</t>
+  </si>
+  <si>
+    <t>0.9839,0.0036,0.0003,0.0053</t>
+  </si>
+  <si>
+    <t>0.6295,0.5437,0.0036,0.0035</t>
+  </si>
+  <si>
+    <t>0.6119,0.5644,0.0014,0.0020</t>
+  </si>
+  <si>
+    <t>0.5185,0.6276,0.0052,0.0024</t>
+  </si>
+  <si>
+    <t>0.3444,0.1525,0.6446,0.0231</t>
+  </si>
+  <si>
+    <t>0.9247,0.0844,0.0082,0.0034</t>
+  </si>
+  <si>
+    <t>0.8071,0.2626,0.0033,0.0051</t>
+  </si>
+  <si>
+    <t>0.9676,0.0470,0.0020,0.0009</t>
+  </si>
+  <si>
+    <t>0.9314,0.1054,0.0058,0.0018</t>
+  </si>
+  <si>
+    <t>0.0015,0.0154,0.9963,0.0002</t>
+  </si>
+  <si>
+    <t>0.8752,0.1692,0.0113,0.0034</t>
+  </si>
+  <si>
+    <t>0.0012,0.0154,0.9913,0.0025</t>
+  </si>
+  <si>
+    <t>0.0070,0.0494,0.9728,0.0064</t>
+  </si>
+  <si>
+    <t>0.1081,0.0117,0.9236,0.0007</t>
+  </si>
+  <si>
+    <t>0.0026,0.2106,0.9728,0.0034</t>
+  </si>
+  <si>
+    <t>0.0219,0.0143,0.9736,0.0016</t>
+  </si>
+  <si>
+    <t>0.0012,0.0006,0.9980,0.0002</t>
+  </si>
+  <si>
+    <t>0.0513,0.0092,0.9426,0.0095</t>
+  </si>
+  <si>
+    <t>0.3302,0.0648,0.6000,0.0036</t>
+  </si>
+  <si>
+    <t>0.1709,0.0125,0.9029,0.0031</t>
+  </si>
+  <si>
+    <t>0.4103,0.1159,0.4810,0.0068</t>
+  </si>
+  <si>
+    <t>0.2823,0.0460,0.6961,0.0009</t>
+  </si>
+  <si>
+    <t>0.2817,0.0292,0.7706,0.0012</t>
+  </si>
+  <si>
+    <t>0.7265,0.0329,0.2996,0.0107</t>
+  </si>
+  <si>
+    <t>0.2858,0.3272,0.4666,0.0146</t>
+  </si>
+  <si>
+    <t>0.7050,0.0442,0.2546,0.0387</t>
+  </si>
+  <si>
+    <t>0.2735,0.8152,0.0039,0.0003</t>
+  </si>
+  <si>
+    <t>0.8726,0.2619,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.9170,0.1375,0.0061,0.0019</t>
+  </si>
+  <si>
+    <t>0.9885,0.0119,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9721,0.0473,0.0021,0.0007</t>
+  </si>
+  <si>
+    <t>0.6334,0.0333,0.3148,0.0676</t>
+  </si>
+  <si>
+    <t>0.6761,0.0174,0.4281,0.0187</t>
+  </si>
+  <si>
+    <t>0.6052,0.0698,0.0696,0.2645</t>
+  </si>
+  <si>
+    <t>0.3055,0.0987,0.5604,0.0051</t>
+  </si>
+  <si>
+    <t>0.6603,0.0770,0.3126,0.0412</t>
+  </si>
+  <si>
+    <t>0.0447,0.1838,0.8185,0.0037</t>
+  </si>
+  <si>
+    <t>0.0066,0.0707,0.9638,0.0056</t>
+  </si>
+  <si>
+    <t>0.0185,0.2547,0.9198,0.0058</t>
+  </si>
+  <si>
+    <t>0.0206,0.2461,0.8774,0.0080</t>
+  </si>
+  <si>
+    <t>0.0233,0.5033,0.6963,0.0071</t>
+  </si>
+  <si>
+    <t>0.9740,0.0088,0.0010,0.0073</t>
+  </si>
+  <si>
+    <t>0.9798,0.0276,0.0009,0.0007</t>
+  </si>
+  <si>
+    <t>0.9761,0.0143,0.0008,0.0033</t>
+  </si>
+  <si>
+    <t>0.9733,0.0421,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.9892,0.0048,0.0003,0.0014</t>
+  </si>
+  <si>
+    <t>0.9901,0.0071,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.9847,0.0084,0.0004,0.0024</t>
+  </si>
+  <si>
+    <t>0.9895,0.0042,0.0002,0.0017</t>
+  </si>
+  <si>
+    <t>0.0103,0.0103,0.9848,0.0022</t>
+  </si>
+  <si>
+    <t>0.2566,0.4816,0.2893,0.0112</t>
+  </si>
+  <si>
+    <t>0.8231,0.0436,0.1409,0.0173</t>
+  </si>
+  <si>
+    <t>0.0022,0.0081,0.9923,0.0015</t>
+  </si>
+  <si>
+    <t>0.0018,0.0023,0.9951,0.0011</t>
+  </si>
+  <si>
+    <t>0.0194,0.0367,0.9654,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9971,0.0047</t>
+  </si>
+  <si>
+    <t>0.0303,0.0235,0.9259,0.0184</t>
+  </si>
+  <si>
+    <t>0.0024,0.0226,0.9921,0.0009</t>
+  </si>
+  <si>
+    <t>0.0097,0.0061,0.9869,0.0012</t>
+  </si>
+  <si>
+    <t>0.2606,0.4547,0.2205,0.0052</t>
+  </si>
+  <si>
+    <t>0.4104,0.0090,0.7319,0.0164</t>
+  </si>
+  <si>
+    <t>0.3670,0.0104,0.7791,0.0057</t>
+  </si>
+  <si>
+    <t>0.6472,0.0100,0.4139,0.0341</t>
+  </si>
+  <si>
+    <t>0.9385,0.0680,0.0073,0.0063</t>
+  </si>
+  <si>
+    <t>0.9928,0.0021,0.0002,0.0016</t>
+  </si>
+  <si>
+    <t>0.9942,0.0029,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9900,0.0057,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9687,0.0254,0.0055,0.0025</t>
+  </si>
+  <si>
+    <t>0.9811,0.0236,0.0018,0.0008</t>
+  </si>
+  <si>
+    <t>0.9871,0.0077,0.0009,0.0020</t>
+  </si>
+  <si>
+    <t>0.9889,0.0077,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.0333,0.2090,0.8346,0.0324</t>
+  </si>
+  <si>
+    <t>0.0022,0.0189,0.9936,0.0003</t>
+  </si>
+  <si>
+    <t>0.0163,0.0088,0.9833,0.0008</t>
+  </si>
+  <si>
+    <t>0.0521,0.0267,0.9333,0.0011</t>
+  </si>
+  <si>
+    <t>0.0046,0.0073,0.9911,0.0013</t>
+  </si>
+  <si>
+    <t>0.0587,0.0244,0.8283,0.1238</t>
+  </si>
+  <si>
+    <t>0.3777,0.0058,0.7723,0.0126</t>
+  </si>
+  <si>
+    <t>0.1184,0.0082,0.6346,0.2481</t>
+  </si>
+  <si>
+    <t>0.3819,0.0009,0.0024,0.8341</t>
+  </si>
+  <si>
+    <t>0.0644,0.2584,0.0329,0.9029</t>
+  </si>
+  <si>
+    <t>0.0464,0.0012,0.0009,0.9856</t>
+  </si>
+  <si>
+    <t>0.0176,0.0002,0.0010,0.9932</t>
+  </si>
+  <si>
+    <t>0.0278,0.0024,0.0024,0.9853</t>
+  </si>
+  <si>
+    <t>0.7222,0.1323,0.1665,0.0222</t>
   </si>
 </sst>
 </file>
@@ -1962,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1976,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,10 +1993,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2004,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2018,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2032,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2046,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2060,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2074,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2088,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2102,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2116,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2130,7 +2136,7 @@
         <v>261</v>
       </c>
       <c r="D14" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2144,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2158,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2172,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2186,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2200,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2214,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2228,7 +2234,7 @@
         <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2242,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2256,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2270,7 +2276,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2284,7 +2290,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2298,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2312,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2326,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2340,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2354,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,10 +2371,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2396,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2410,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2424,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,10 +2441,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D36" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,10 +2455,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D37" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2466,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2480,7 +2486,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,10 +2497,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2508,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,10 +2525,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D42" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2536,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2550,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2564,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2575,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="D46" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2592,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2606,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2620,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2634,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2648,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2662,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2676,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2690,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2704,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2718,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2732,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2746,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2760,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2774,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2788,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2802,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,10 +2819,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2830,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2844,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2858,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2872,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2886,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2900,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,10 +2917,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2928,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2942,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2956,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2970,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2984,7 +2990,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2998,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3012,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3026,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3040,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3054,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3068,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3082,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,10 +3099,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3110,7 +3116,7 @@
         <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,10 +3127,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3138,7 +3144,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,10 +3155,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,10 +3169,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3180,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3194,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3208,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3222,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3236,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3250,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3264,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3278,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3292,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3306,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3320,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3334,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3348,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3362,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3376,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3390,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3404,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3418,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,10 +3435,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D107" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3446,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3460,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3474,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3488,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3502,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,10 +3519,10 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D113" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3530,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3544,7 +3550,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3558,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3572,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3600,7 +3606,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,10 +3617,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3628,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3642,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3656,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3670,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3684,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3698,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,10 +3715,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3726,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3740,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3754,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3768,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3782,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3796,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3810,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3824,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3838,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3852,7 +3858,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3866,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3880,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3894,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3908,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,10 +3925,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D142" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3936,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3950,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3964,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3978,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3992,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4006,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4020,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4034,7 +4040,7 @@
         <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4048,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4062,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4076,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4090,7 +4096,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4104,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4118,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4132,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4146,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,10 +4163,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4174,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4188,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4216,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4230,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4244,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4258,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4272,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4286,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4300,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4314,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4328,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4342,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,10 +4359,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D173" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,10 +4373,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D174" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,10 +4387,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D175" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4412,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4426,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4440,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4454,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4468,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4482,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4496,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4510,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4524,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4538,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4552,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4566,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4580,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4594,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4608,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D192" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4636,7 +4642,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4650,7 +4656,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4664,7 +4670,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,10 +4681,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D196" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,10 +4695,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,10 +4709,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4720,7 +4726,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4734,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4748,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,10 +4765,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4776,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4790,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4804,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4818,7 +4824,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,10 +4835,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4846,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4860,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4874,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4888,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,10 +4905,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4916,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4930,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4944,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4958,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4972,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4986,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5000,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5014,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5028,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5039,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D222" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5056,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5070,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5084,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5098,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5112,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5126,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5140,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5154,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,10 +5171,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D231" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,10 +5185,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5210,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5224,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5238,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5252,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5266,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5280,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5294,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5308,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5322,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5336,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5350,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5364,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5378,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5392,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5420,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5434,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,10 +5451,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5462,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5476,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5490,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5504,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5518,7 +5524,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
